--- a/api/templates/device_capacity/es.xlsx
+++ b/api/templates/device_capacity/es.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_capacity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A08E78C-13F8-47D0-9DDA-F74D0F38C43E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3AA4B0-D08F-4438-9911-1DCCA419D6E0}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35571" yWindow="1329" windowWidth="22989" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="1" r:id="rId1"/>
@@ -20,27 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>&lt;serial&gt;</t>
-  </si>
-  <si>
     <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;lastUploadOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;deviceApprovalStatus&gt;</t>
-  </si>
-  <si>
-    <t>&lt;deviceMaintenanceStatus&gt;</t>
-  </si>
-  <si>
-    <t>Actividad de dispositivos</t>
   </si>
   <si>
     <t>Entre fechas: &lt;Dates&gt;</t>
@@ -55,25 +40,13 @@
     <t>Dispositivos</t>
   </si>
   <si>
-    <t>Nro. De serie</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Estado de mantenimiento</t>
-  </si>
-  <si>
-    <t>Última Carga</t>
+    <t>Capacidad de dispositivos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -195,13 +168,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -583,88 +555,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.35546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="6" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>4</v>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
